--- a/PCB引脚说明.xlsx
+++ b/PCB引脚说明.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="149">
   <si>
     <t>STM32F103C8T6引脚定义表</t>
   </si>
@@ -146,6 +146,9 @@
     <t>USART2_RTS/ADC12_IN1/TIM2_CH2</t>
   </si>
   <si>
+    <t>ADC</t>
+  </si>
+  <si>
     <t xml:space="preserve">PA2 </t>
   </si>
   <si>
@@ -155,6 +158,9 @@
     <t>副</t>
   </si>
   <si>
+    <t>/</t>
+  </si>
+  <si>
     <t xml:space="preserve">PA3 </t>
   </si>
   <si>
@@ -182,6 +188,9 @@
     <t>TIM1_BKIN</t>
   </si>
   <si>
+    <t>pwm</t>
+  </si>
+  <si>
     <t xml:space="preserve">PA7 </t>
   </si>
   <si>
@@ -227,6 +236,9 @@
     <t>TIM2_CH3</t>
   </si>
   <si>
+    <t>led</t>
+  </si>
+  <si>
     <t xml:space="preserve">PB11 </t>
   </si>
   <si>
@@ -374,6 +386,12 @@
     <t>PB4/TIM3_CH1/SPI1_MISO</t>
   </si>
   <si>
+    <t>温度</t>
+  </si>
+  <si>
+    <t>T_SCL</t>
+  </si>
+  <si>
     <t xml:space="preserve">PB5 </t>
   </si>
   <si>
@@ -383,6 +401,9 @@
     <t>TIM3_CH2/SPI1_MOSI</t>
   </si>
   <si>
+    <t>T_SDA</t>
+  </si>
+  <si>
     <t xml:space="preserve">PB6 </t>
   </si>
   <si>
@@ -395,6 +416,9 @@
     <t>磁编码器</t>
   </si>
   <si>
+    <t>C_SCL</t>
+  </si>
+  <si>
     <t xml:space="preserve">PB7 </t>
   </si>
   <si>
@@ -404,6 +428,9 @@
     <t>USART1_RX</t>
   </si>
   <si>
+    <t>C_SDA</t>
+  </si>
+  <si>
     <t xml:space="preserve">BOOT0 </t>
   </si>
   <si>
@@ -422,6 +449,9 @@
     <t>OLED</t>
   </si>
   <si>
+    <t>OLED_SCL</t>
+  </si>
+  <si>
     <t xml:space="preserve">PB9 </t>
   </si>
   <si>
@@ -429,6 +459,9 @@
   </si>
   <si>
     <t>I2C1_SDA/CAN_TX</t>
+  </si>
+  <si>
+    <t>OLED_SDA</t>
   </si>
   <si>
     <t xml:space="preserve">VSS_3 </t>
@@ -453,7 +486,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -485,6 +518,26 @@
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -972,137 +1025,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1143,6 +1196,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1466,7 +1528,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultColWidth="16.6283185840708" defaultRowHeight="19.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.3716814159292" style="1" customWidth="1"/>
@@ -1716,204 +1778,218 @@
       <c r="I12" s="3"/>
     </row>
     <row r="13" customHeight="1" spans="1:9">
-      <c r="A13" s="12">
+      <c r="A13" s="14">
         <v>11</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12" t="s">
+      <c r="C13" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14" t="s">
+        <v>39</v>
+      </c>
       <c r="I13" s="3"/>
     </row>
     <row r="14" customHeight="1" spans="1:9">
-      <c r="A14" s="12">
+      <c r="A14" s="14">
         <v>12</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="12" t="s">
+      <c r="B14" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3" t="s">
+      <c r="C14" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="3"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
-      <c r="A15" s="12">
-        <v>13</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="A15" s="14">
+        <v>13</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="12" t="s">
+      <c r="I15" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="3"/>
     </row>
     <row r="16" customHeight="1" spans="1:9">
-      <c r="A16" s="12">
+      <c r="A16" s="14">
         <v>14</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="3"/>
+      <c r="B16" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="14"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row r="17" customHeight="1" spans="1:9">
-      <c r="A17" s="12">
+      <c r="A17" s="14">
         <v>15</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="3"/>
+      <c r="B17" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="14"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row r="18" customHeight="1" spans="1:9">
-      <c r="A18" s="12">
+      <c r="A18" s="14">
         <v>16</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="12" t="s">
+      <c r="B18" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="H18" s="3"/>
+      <c r="C18" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="I18" s="3"/>
     </row>
     <row r="19" customHeight="1" spans="1:9">
-      <c r="A19" s="12">
+      <c r="A19" s="14">
         <v>17</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" s="12" t="s">
+      <c r="B19" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="H19" s="3"/>
       <c r="I19" s="3"/>
     </row>
     <row r="20" customHeight="1" spans="1:9">
-      <c r="A20" s="12">
+      <c r="A20" s="14">
         <v>18</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H20" s="3"/>
+      <c r="B20" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="I20" s="3"/>
     </row>
     <row r="21" customHeight="1" spans="1:9">
-      <c r="A21" s="12">
+      <c r="A21" s="14">
         <v>19</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H21" s="3"/>
+      <c r="B21" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="I21" s="3"/>
     </row>
     <row r="22" customHeight="1" spans="1:9">
@@ -1921,16 +1997,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -1938,51 +2014,53 @@
       <c r="I22" s="3"/>
     </row>
     <row r="23" customHeight="1" spans="1:9">
-      <c r="A23" s="12">
+      <c r="A23" s="14">
         <v>21</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23" s="12" t="s">
+      <c r="B23" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="E23" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="I23" s="14"/>
     </row>
     <row r="24" customHeight="1" spans="1:9">
       <c r="A24" s="12">
         <v>22</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -1992,14 +2070,14 @@
         <v>8</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
@@ -2011,14 +2089,14 @@
         <v>8</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
@@ -2030,19 +2108,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -2053,19 +2131,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -2076,19 +2154,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -2099,19 +2177,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -2122,92 +2200,98 @@
         <v>29</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
-    <row r="32" customHeight="1" spans="1:9">
-      <c r="A32" s="12">
+    <row r="32" customHeight="1" spans="1:10">
+      <c r="A32" s="14">
         <v>30</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I32" s="3"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:9">
-      <c r="A33" s="12">
+      <c r="B32" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J32" s="16"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:10">
+      <c r="A33" s="14">
         <v>31</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I33" s="3"/>
+      <c r="B33" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J33" s="16"/>
     </row>
     <row r="34" customHeight="1" spans="1:9">
       <c r="A34" s="12">
         <v>32</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
@@ -2218,19 +2302,19 @@
         <v>33</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
@@ -2241,20 +2325,20 @@
         <v>8</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>13</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F36" s="11"/>
       <c r="G36" s="10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -2264,14 +2348,14 @@
         <v>8</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
@@ -2283,14 +2367,14 @@
         <v>8</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -2302,20 +2386,20 @@
         <v>8</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F39" s="11"/>
       <c r="G39" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -2325,20 +2409,20 @@
         <v>38</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="12" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -2348,137 +2432,149 @@
         <v>39</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="12" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row r="42" customHeight="1" spans="1:9">
-      <c r="A42" s="12">
+      <c r="A42" s="14">
         <v>40</v>
       </c>
-      <c r="B42" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
+      <c r="B42" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="43" customHeight="1" spans="1:9">
-      <c r="A43" s="12">
+      <c r="A43" s="14">
         <v>41</v>
       </c>
-      <c r="B43" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+      <c r="B43" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="44" customHeight="1" spans="1:9">
-      <c r="A44" s="12">
+      <c r="A44" s="14">
         <v>42</v>
       </c>
-      <c r="B44" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I44" s="3"/>
+      <c r="B44" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="45" customHeight="1" spans="1:9">
-      <c r="A45" s="12">
+      <c r="A45" s="14">
         <v>43</v>
       </c>
-      <c r="B45" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I45" s="3"/>
+      <c r="B45" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="46" customHeight="1" spans="1:9">
       <c r="A46" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D46" s="10"/>
       <c r="E46" s="10" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F46" s="11"/>
       <c r="G46" s="11"/>
@@ -2486,72 +2582,76 @@
       <c r="I46" s="3"/>
     </row>
     <row r="47" customHeight="1" spans="1:9">
-      <c r="A47" s="12">
+      <c r="A47" s="14">
         <v>45</v>
       </c>
-      <c r="B47" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I47" s="3"/>
+      <c r="B47" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="48" customHeight="1" spans="1:9">
-      <c r="A48" s="12">
+      <c r="A48" s="14">
         <v>46</v>
       </c>
-      <c r="B48" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I48" s="3"/>
+      <c r="B48" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="49" customHeight="1" spans="1:9">
       <c r="A49" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
@@ -2563,14 +2663,14 @@
         <v>8</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>

--- a/PCB引脚说明.xlsx
+++ b/PCB引脚说明.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="9555"/>
+    <workbookView windowWidth="8497" windowHeight="7477"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1801,9 +1801,7 @@
       <c r="I13" s="3"/>
     </row>
     <row r="14" customHeight="1" spans="1:9">
-      <c r="A14" s="14">
-        <v>12</v>
-      </c>
+      <c r="A14" s="14"/>
       <c r="B14" s="15" t="s">
         <v>40</v>
       </c>
@@ -1826,9 +1824,7 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
-      <c r="A15" s="14">
-        <v>13</v>
-      </c>
+      <c r="A15" s="14"/>
       <c r="B15" s="15" t="s">
         <v>44</v>
       </c>
@@ -1893,9 +1889,7 @@
       <c r="I17" s="3"/>
     </row>
     <row r="18" customHeight="1" spans="1:9">
-      <c r="A18" s="14">
-        <v>16</v>
-      </c>
+      <c r="A18" s="14"/>
       <c r="B18" s="15" t="s">
         <v>50</v>
       </c>
@@ -1918,9 +1912,7 @@
       <c r="I18" s="3"/>
     </row>
     <row r="19" customHeight="1" spans="1:9">
-      <c r="A19" s="14">
-        <v>17</v>
-      </c>
+      <c r="A19" s="14"/>
       <c r="B19" s="15" t="s">
         <v>54</v>
       </c>
@@ -1943,9 +1935,7 @@
       <c r="I19" s="3"/>
     </row>
     <row r="20" customHeight="1" spans="1:9">
-      <c r="A20" s="14">
-        <v>18</v>
-      </c>
+      <c r="A20" s="14"/>
       <c r="B20" s="15" t="s">
         <v>57</v>
       </c>
@@ -1968,9 +1958,7 @@
       <c r="I20" s="3"/>
     </row>
     <row r="21" customHeight="1" spans="1:9">
-      <c r="A21" s="14">
-        <v>19</v>
-      </c>
+      <c r="A21" s="14"/>
       <c r="B21" s="15" t="s">
         <v>60</v>
       </c>
@@ -2014,9 +2002,7 @@
       <c r="I22" s="3"/>
     </row>
     <row r="23" customHeight="1" spans="1:9">
-      <c r="A23" s="14">
-        <v>21</v>
-      </c>
+      <c r="A23" s="14"/>
       <c r="B23" s="15" t="s">
         <v>66</v>
       </c>
@@ -2219,9 +2205,7 @@
       <c r="I31" s="3"/>
     </row>
     <row r="32" customHeight="1" spans="1:10">
-      <c r="A32" s="14">
-        <v>30</v>
-      </c>
+      <c r="A32" s="14"/>
       <c r="B32" s="15" t="s">
         <v>89</v>
       </c>
@@ -2247,9 +2231,7 @@
       <c r="J32" s="16"/>
     </row>
     <row r="33" customHeight="1" spans="1:10">
-      <c r="A33" s="14">
-        <v>31</v>
-      </c>
+      <c r="A33" s="14"/>
       <c r="B33" s="15" t="s">
         <v>92</v>
       </c>
@@ -2451,9 +2433,7 @@
       <c r="I41" s="3"/>
     </row>
     <row r="42" customHeight="1" spans="1:9">
-      <c r="A42" s="14">
-        <v>40</v>
-      </c>
+      <c r="A42" s="14"/>
       <c r="B42" s="14" t="s">
         <v>116</v>
       </c>
@@ -2478,9 +2458,7 @@
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:9">
-      <c r="A43" s="14">
-        <v>41</v>
-      </c>
+      <c r="A43" s="14"/>
       <c r="B43" s="15" t="s">
         <v>121</v>
       </c>
@@ -2505,9 +2483,7 @@
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:9">
-      <c r="A44" s="14">
-        <v>42</v>
-      </c>
+      <c r="A44" s="14"/>
       <c r="B44" s="15" t="s">
         <v>125</v>
       </c>
@@ -2534,9 +2510,7 @@
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:9">
-      <c r="A45" s="14">
-        <v>43</v>
-      </c>
+      <c r="A45" s="14"/>
       <c r="B45" s="15" t="s">
         <v>130</v>
       </c>
@@ -2582,9 +2556,7 @@
       <c r="I46" s="3"/>
     </row>
     <row r="47" customHeight="1" spans="1:9">
-      <c r="A47" s="14">
-        <v>45</v>
-      </c>
+      <c r="A47" s="14"/>
       <c r="B47" s="15" t="s">
         <v>136</v>
       </c>
@@ -2611,9 +2583,7 @@
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:9">
-      <c r="A48" s="14">
-        <v>46</v>
-      </c>
+      <c r="A48" s="14"/>
       <c r="B48" s="15" t="s">
         <v>141</v>
       </c>

--- a/PCB引脚说明.xlsx
+++ b/PCB引脚说明.xlsx
@@ -1778,9 +1778,7 @@
       <c r="I12" s="3"/>
     </row>
     <row r="13" customHeight="1" spans="1:9">
-      <c r="A13" s="14">
-        <v>11</v>
-      </c>
+      <c r="A13" s="14"/>
       <c r="B13" s="15" t="s">
         <v>37</v>
       </c>
